--- a/deliverable/学生发表论文_已填.xlsx
+++ b/deliverable/学生发表论文_已填.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>沈亮</t>
+          <t>申亮</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -618,11 +618,6 @@
       </c>
       <c r="M2" s="5" t="n">
         <v>46264</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>DOI 10.1016/j.foodchem.2026.149910；WOS入藏号 001612255000001；录用 2026-06-03；被引 0；共同第一作者：文绍华、马慧珂；通讯作者：沈亮</t>
-        </is>
       </c>
     </row>
   </sheetData>
